--- a/util/fitaero/example/Example_Initdis_Simplex.xlsx
+++ b/util/fitaero/example/Example_Initdis_Simplex.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="86">
   <si>
     <t xml:space="preserve">URBAN BACKGROUND AEROSOL</t>
   </si>
@@ -169,6 +169,12 @@
     <t xml:space="preserve">./output/out_sizedis.dat</t>
   </si>
   <si>
+    <t xml:space="preserve">FINE SET / URBAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">init1, RH=50%</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mode 2: 10-31 nm</t>
   </si>
   <si>
@@ -209,6 +215,9 @@
   </si>
   <si>
     <t xml:space="preserve">BETA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate = initial estimate of fitaero</t>
   </si>
   <si>
     <t xml:space="preserve">Mode 3: 10-31 nm</t>
@@ -592,7 +601,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart85.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -638,10 +647,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0696122860020141"/>
-          <c:y val="0.213320104179586"/>
-          <c:w val="0.717522658610272"/>
-          <c:h val="0.67853156393402"/>
+          <c:x val="0.0696079048398263"/>
+          <c:y val="0.213346564128008"/>
+          <c:w val="0.717477500157342"/>
+          <c:h val="0.678491689407095"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -701,7 +710,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$5:$U$5</c:f>
+              <c:f>Test_Initdis!$D$6:$U$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
@@ -737,7 +746,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$3:$U$3</c:f>
+              <c:f>Test_Initdis!$D$4:$U$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
@@ -778,7 +787,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Test_Initdis!$B$4:$B$4</c:f>
+              <c:f>Test_Initdis!$B$5:$B$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -830,83 +839,83 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
+              <c:f>Test_Initdis!$D$6:$U$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>10.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
               <c:f>Test_Initdis!$D$5:$U$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>10.4</c:v>
+                  <c:v>181.06</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.1</c:v>
+                  <c:v>303.46</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>399.67</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.9</c:v>
+                  <c:v>495.33</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13.8</c:v>
+                  <c:v>713.76</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.9</c:v>
+                  <c:v>825.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16</c:v>
+                  <c:v>991.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>17.2</c:v>
+                  <c:v>1050.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>18.4</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Test_Initdis!$D$4:$U$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>597.53</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>795.14</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>802.51</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>784.6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>913.96</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>838.39</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>819.06</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>819.06</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>710.8</c:v>
+                  <c:v>1248.77</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="36388891"/>
-        <c:axId val="86148279"/>
+        <c:axId val="96697566"/>
+        <c:axId val="12173569"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="36388891"/>
+        <c:axId val="96697566"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -938,12 +947,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86148279"/>
+        <c:crossAx val="12173569"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="86148279"/>
+        <c:axId val="12173569"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -985,7 +994,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36388891"/>
+        <c:crossAx val="96697566"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1041,7 +1050,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart86.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1087,10 +1096,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0665464270166055"/>
-          <c:y val="0.215852015190494"/>
-          <c:w val="0.709870016792089"/>
-          <c:h val="0.685777287761852"/>
+          <c:x val="0.0665422885572139"/>
+          <c:y val="0.21587846116148"/>
+          <c:w val="0.709825870646766"/>
+          <c:h val="0.685738789512374"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -1150,7 +1159,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$29:$U$29</c:f>
+              <c:f>Test_Initdis!$D$30:$U$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
@@ -1213,7 +1222,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$27:$U$27</c:f>
+              <c:f>Test_Initdis!$D$28:$U$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
@@ -1281,7 +1290,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Test_Initdis!$B$28:$B$28</c:f>
+              <c:f>Test_Initdis!$B$29:$B$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1333,137 +1342,137 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
+              <c:f>Test_Initdis!$D$30:$U$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>72.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>77.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>83.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>96.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>103.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>111.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>119.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>128.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>138.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>148.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>159.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>171.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>184.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>198.1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>212.9</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>228.8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>245.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
               <c:f>Test_Initdis!$D$29:$U$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>72.3</c:v>
+                  <c:v>424.19</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>77.7</c:v>
+                  <c:v>415.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>83.5</c:v>
+                  <c:v>408.74</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>89.8</c:v>
+                  <c:v>389.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>96.5</c:v>
+                  <c:v>371.88</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>103.7</c:v>
+                  <c:v>350.35</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>111.4</c:v>
+                  <c:v>329.95</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>119.7</c:v>
+                  <c:v>306.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>128.6</c:v>
+                  <c:v>283.51</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>138.2</c:v>
+                  <c:v>261.11</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>148.6</c:v>
+                  <c:v>232.39</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>159.6</c:v>
+                  <c:v>210.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>171.5</c:v>
+                  <c:v>187.24</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>184.3</c:v>
+                  <c:v>165.62</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>198.1</c:v>
+                  <c:v>144.35</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>212.9</c:v>
+                  <c:v>124.96</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>228.8</c:v>
+                  <c:v>106.71</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>245.8</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Test_Initdis!$D$28:$U$28</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>397.61</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>399.99</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>402.51</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>391.88</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>381.65</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>365.87</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>349.87</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>329.08</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>308.07</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>286.34</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>256.67</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>233.38</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>208.45</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>184.55</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>160.65</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>138.62</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>117.75</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>100.26</c:v>
+                  <c:v>91.54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="14680635"/>
-        <c:axId val="21542560"/>
+        <c:axId val="38826433"/>
+        <c:axId val="25045380"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="14680635"/>
+        <c:axId val="38826433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="30"/>
@@ -1496,12 +1505,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21542560"/>
+        <c:crossAx val="25045380"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="21542560"/>
+        <c:axId val="25045380"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1543,7 +1552,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14680635"/>
+        <c:crossAx val="38826433"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1599,7 +1608,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart87.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1634,8 +1643,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.430498824111895"/>
-          <c:y val="0.0369043353636689"/>
+          <c:x val="0.430472182684572"/>
+          <c:y val="0.0370281892021022"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1653,10 +1662,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0664067335066221"/>
-          <c:y val="0.213901827302042"/>
-          <c:w val="0.713516524322317"/>
-          <c:h val="0.688403200764362"/>
+          <c:x val="0.0664026239247478"/>
+          <c:y val="0.213927376970855"/>
+          <c:w val="0.713472368339625"/>
+          <c:h val="0.688365981844243"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -1716,7 +1725,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$41:$L$41</c:f>
+              <c:f>Test_Initdis!$D$42:$L$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1752,7 +1761,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$39:$L$39</c:f>
+              <c:f>Test_Initdis!$D$40:$L$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1793,7 +1802,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Test_Initdis!$B$40:$B$40</c:f>
+              <c:f>Test_Initdis!$B$41:$B$41</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1845,83 +1854,83 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
+              <c:f>Test_Initdis!$D$42:$L$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>264.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>283.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>305.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>327.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>352.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>378.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>406.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>437.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>469.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
               <c:f>Test_Initdis!$D$41:$L$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>264.2</c:v>
+                  <c:v>19.59</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>283.9</c:v>
+                  <c:v>19.63</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>305.1</c:v>
+                  <c:v>19.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>327.8</c:v>
+                  <c:v>18.89</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>352.3</c:v>
+                  <c:v>18.13</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>378.6</c:v>
+                  <c:v>17.16</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>406.8</c:v>
+                  <c:v>16.07</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>437.1</c:v>
+                  <c:v>14.91</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>469.8</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Test_Initdis!$D$40:$L$40</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>26.1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>23.34</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>17.92</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>15.36</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>12.98</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10.85</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>6.81</c:v>
+                  <c:v>12.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="14510403"/>
-        <c:axId val="24114203"/>
+        <c:axId val="17662410"/>
+        <c:axId val="81260542"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="14510403"/>
+        <c:axId val="17662410"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1953,12 +1962,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24114203"/>
+        <c:crossAx val="81260542"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="24114203"/>
+        <c:axId val="81260542"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2000,7 +2009,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14510403"/>
+        <c:crossAx val="17662410"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2056,7 +2065,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart88.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2102,10 +2111,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.066424807808586"/>
-          <c:y val="0.15186683973429"/>
-          <c:w val="0.713570009501598"/>
-          <c:h val="0.688478277468122"/>
+          <c:x val="0.0664219391060246"/>
+          <c:y val="0.151878436163714"/>
+          <c:w val="0.71353919239905"/>
+          <c:h val="0.688454489920586"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -2116,7 +2125,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Test_Initdis!$B$127:$B$127</c:f>
+              <c:f>Test_Initdis!$B$128:$B$128</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2165,7 +2174,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$130:$BE$130</c:f>
+              <c:f>Test_Initdis!$D$131:$BE$131</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
@@ -2336,7 +2345,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$127:$BE$127</c:f>
+              <c:f>Test_Initdis!$D$128:$BE$128</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
@@ -2512,7 +2521,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Test_Initdis!$B$128:$B$128</c:f>
+              <c:f>Test_Initdis!$B$129:$B$129</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2564,7 +2573,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$130:$BE$130</c:f>
+              <c:f>Test_Initdis!$D$131:$BE$131</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
@@ -2735,171 +2744,171 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$128:$BE$128</c:f>
+              <c:f>Test_Initdis!$D$129:$BE$129</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
                 <c:pt idx="0">
-                  <c:v>597.53</c:v>
+                  <c:v>181.06</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>795.14</c:v>
+                  <c:v>303.46</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>802.51</c:v>
+                  <c:v>399.67</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>784.6</c:v>
+                  <c:v>495.33</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>913.96</c:v>
+                  <c:v>713.76</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>838.39</c:v>
+                  <c:v>825.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>819.06</c:v>
+                  <c:v>991.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>819.06</c:v>
+                  <c:v>1050.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>710.8</c:v>
+                  <c:v>1248.77</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>347.56</c:v>
+                  <c:v>173.01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>386.2</c:v>
+                  <c:v>197.71</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>422.21</c:v>
+                  <c:v>222.65</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>454.45</c:v>
+                  <c:v>247.26</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>507.34</c:v>
+                  <c:v>285.18</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>528.94</c:v>
+                  <c:v>308.12</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>568.58</c:v>
+                  <c:v>343.59</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>575.19</c:v>
+                  <c:v>361.52</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>620.67</c:v>
+                  <c:v>406.04</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>608.71</c:v>
+                  <c:v>416.06</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>610.75</c:v>
+                  <c:v>436.31</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>621.99</c:v>
+                  <c:v>465.21</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>602.39</c:v>
+                  <c:v>473.14</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>575.34</c:v>
+                  <c:v>475.13</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>570.31</c:v>
+                  <c:v>495.72</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>526.85</c:v>
+                  <c:v>483.7</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>502.86</c:v>
+                  <c:v>487.91</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>460.56</c:v>
+                  <c:v>473.6</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>397.61</c:v>
+                  <c:v>424.19</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>399.99</c:v>
+                  <c:v>415.9</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>402.51</c:v>
+                  <c:v>408.74</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>391.88</c:v>
+                  <c:v>389.35</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>381.65</c:v>
+                  <c:v>371.88</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>365.87</c:v>
+                  <c:v>350.35</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>349.87</c:v>
+                  <c:v>329.95</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>329.08</c:v>
+                  <c:v>306.25</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>308.07</c:v>
+                  <c:v>283.51</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>286.34</c:v>
+                  <c:v>261.11</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>256.67</c:v>
+                  <c:v>232.39</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>233.38</c:v>
+                  <c:v>210.25</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>208.45</c:v>
+                  <c:v>187.24</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>184.55</c:v>
+                  <c:v>165.62</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>160.65</c:v>
+                  <c:v>144.35</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>138.62</c:v>
+                  <c:v>124.96</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>117.75</c:v>
+                  <c:v>106.71</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>100.26</c:v>
+                  <c:v>91.54</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>26.1</c:v>
+                  <c:v>19.59</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>23.34</c:v>
+                  <c:v>19.63</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>20.5</c:v>
+                  <c:v>19.3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>17.92</c:v>
+                  <c:v>18.89</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>15.36</c:v>
+                  <c:v>18.13</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>12.98</c:v>
+                  <c:v>17.16</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>10.85</c:v>
+                  <c:v>16.07</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>9</c:v>
+                  <c:v>14.91</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>6.81</c:v>
+                  <c:v>12.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2911,7 +2920,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Test_Initdis!$B$129:$B$129</c:f>
+              <c:f>Test_Initdis!$B$130:$B$130</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2963,353 +2972,353 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
+              <c:f>Test_Initdis!$D$131:$BE$131</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="54"/>
+                <c:pt idx="0">
+                  <c:v>10.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22.9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>24.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>26.4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>28.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>32.8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>35.2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>37.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>40.7</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>43.7</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>50.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>54.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>58.3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>62.6</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>67.3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>72.3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>77.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>83.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>89.8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>96.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>103.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>111.4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>119.7</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>128.6</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>138.2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>148.6</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>159.6</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>171.5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>184.3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>198.1</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>212.9</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>228.8</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>245.8</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>264.2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>283.9</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>305.1</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>327.8</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>352.3</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>378.6</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>406.8</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>437.1</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>469.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
               <c:f>Test_Initdis!$D$130:$BE$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
                 <c:pt idx="0">
-                  <c:v>10.4</c:v>
+                  <c:v>127.807058823529</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.1</c:v>
+                  <c:v>214.207058823529</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>282.12</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.9</c:v>
+                  <c:v>349.644705882353</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13.8</c:v>
+                  <c:v>503.830588235294</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.9</c:v>
+                  <c:v>582.847058823529</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16</c:v>
+                  <c:v>699.670588235294</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>17.2</c:v>
+                  <c:v>741.529411764706</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>18.4</c:v>
+                  <c:v>881.484705882353</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.8</c:v>
+                  <c:v>242.214</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21.3</c:v>
+                  <c:v>276.794</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>22.9</c:v>
+                  <c:v>311.71</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>24.6</c:v>
+                  <c:v>346.164</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>26.4</c:v>
+                  <c:v>399.252</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>28.4</c:v>
+                  <c:v>431.368</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>30.5</c:v>
+                  <c:v>481.026</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>32.8</c:v>
+                  <c:v>506.128</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>35.2</c:v>
+                  <c:v>568.456</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>37.9</c:v>
+                  <c:v>582.484</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>40.7</c:v>
+                  <c:v>610.834</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>43.7</c:v>
+                  <c:v>651.294</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>47</c:v>
+                  <c:v>662.396</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>50.5</c:v>
+                  <c:v>665.182</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>54.2</c:v>
+                  <c:v>694.008</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>58.3</c:v>
+                  <c:v>677.18</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>62.6</c:v>
+                  <c:v>683.074</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>67.3</c:v>
+                  <c:v>663.04</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>72.3</c:v>
+                  <c:v>522.08</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>77.7</c:v>
+                  <c:v>511.876923076923</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>83.5</c:v>
+                  <c:v>503.064615384615</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>89.8</c:v>
+                  <c:v>479.2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>96.5</c:v>
+                  <c:v>457.698461538462</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>103.7</c:v>
+                  <c:v>431.2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>111.4</c:v>
+                  <c:v>406.092307692308</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>119.7</c:v>
+                  <c:v>376.923076923077</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>128.6</c:v>
+                  <c:v>348.935384615385</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>138.2</c:v>
+                  <c:v>321.366153846154</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>148.6</c:v>
+                  <c:v>286.018461538462</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>159.6</c:v>
+                  <c:v>258.769230769231</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>171.5</c:v>
+                  <c:v>230.449230769231</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>184.3</c:v>
+                  <c:v>203.84</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>198.1</c:v>
+                  <c:v>177.661538461538</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>212.9</c:v>
+                  <c:v>153.796923076923</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>228.8</c:v>
+                  <c:v>131.335384615385</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>245.8</c:v>
+                  <c:v>112.664615384615</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>264.2</c:v>
+                  <c:v>19.59</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>283.9</c:v>
+                  <c:v>19.63</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>305.1</c:v>
+                  <c:v>19.3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>327.8</c:v>
+                  <c:v>18.89</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>352.3</c:v>
+                  <c:v>18.13</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>378.6</c:v>
+                  <c:v>17.16</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>406.8</c:v>
+                  <c:v>16.07</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>437.1</c:v>
+                  <c:v>14.91</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>469.8</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Test_Initdis!$D$129:$BE$129</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
-                <c:pt idx="0">
-                  <c:v>478.024</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>636.112</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>642.008</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>627.68</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>731.168</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>670.712</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>655.248</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>655.248</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>568.64</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>347.56</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>386.2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>422.21</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>454.45</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>507.34</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>528.94</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>568.58</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>575.19</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>620.67</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>608.71</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>610.75</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>621.99</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>602.39</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>575.34</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>570.31</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>526.85</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>502.86</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>460.56</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>530.146666666667</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>533.32</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>536.68</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>522.506666666667</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>508.866666666667</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>487.826666666667</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>466.493333333333</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>438.773333333333</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>410.76</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>381.786666666667</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>342.226666666667</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>311.173333333333</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>277.933333333333</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>246.066666666667</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>214.2</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>184.826666666667</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>157</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>133.68</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>30.1153846153846</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>26.9307692307692</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>23.6538461538462</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>20.6769230769231</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>17.7230769230769</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>14.9769230769231</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>12.5192307692308</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>10.3846153846154</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>7.85769230769231</c:v>
+                  <c:v>12.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="30302078"/>
-        <c:axId val="72536676"/>
+        <c:axId val="59675563"/>
+        <c:axId val="60800561"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="30302078"/>
+        <c:axId val="59675563"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -3346,8 +3355,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.602746825602488"/>
-              <c:y val="0.920592502099717"/>
+              <c:x val="0.602720794644785"/>
+              <c:y val="0.920510079413561"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -3384,12 +3393,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72536676"/>
+        <c:crossAx val="60800561"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="72536676"/>
+        <c:axId val="60800561"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3431,7 +3440,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30302078"/>
+        <c:crossAx val="59675563"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3487,7 +3496,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart89.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -3533,10 +3542,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0663999652128538"/>
-          <c:y val="0.151940475183901"/>
-          <c:w val="0.71361481932426"/>
-          <c:h val="0.688424790733068"/>
+          <c:x val="0.0663970780067832"/>
+          <c:y val="0.1519533231862"/>
+          <c:w val="0.713583789894773"/>
+          <c:h val="0.688398444106207"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -3547,7 +3556,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Test_Initdis!$B$127:$B$127</c:f>
+              <c:f>Test_Initdis!$B$128:$B$128</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3596,7 +3605,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$130:$BE$130</c:f>
+              <c:f>Test_Initdis!$D$131:$BE$131</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
@@ -3767,7 +3776,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$127:$BE$127</c:f>
+              <c:f>Test_Initdis!$D$128:$BE$128</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
@@ -3943,7 +3952,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Test_Initdis!$B$128:$B$128</c:f>
+              <c:f>Test_Initdis!$B$129:$B$129</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3995,7 +4004,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$130:$BE$130</c:f>
+              <c:f>Test_Initdis!$D$131:$BE$131</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
@@ -4166,171 +4175,171 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$128:$BE$128</c:f>
+              <c:f>Test_Initdis!$D$129:$BE$129</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
                 <c:pt idx="0">
-                  <c:v>597.53</c:v>
+                  <c:v>181.06</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>795.14</c:v>
+                  <c:v>303.46</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>802.51</c:v>
+                  <c:v>399.67</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>784.6</c:v>
+                  <c:v>495.33</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>913.96</c:v>
+                  <c:v>713.76</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>838.39</c:v>
+                  <c:v>825.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>819.06</c:v>
+                  <c:v>991.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>819.06</c:v>
+                  <c:v>1050.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>710.8</c:v>
+                  <c:v>1248.77</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>347.56</c:v>
+                  <c:v>173.01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>386.2</c:v>
+                  <c:v>197.71</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>422.21</c:v>
+                  <c:v>222.65</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>454.45</c:v>
+                  <c:v>247.26</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>507.34</c:v>
+                  <c:v>285.18</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>528.94</c:v>
+                  <c:v>308.12</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>568.58</c:v>
+                  <c:v>343.59</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>575.19</c:v>
+                  <c:v>361.52</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>620.67</c:v>
+                  <c:v>406.04</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>608.71</c:v>
+                  <c:v>416.06</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>610.75</c:v>
+                  <c:v>436.31</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>621.99</c:v>
+                  <c:v>465.21</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>602.39</c:v>
+                  <c:v>473.14</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>575.34</c:v>
+                  <c:v>475.13</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>570.31</c:v>
+                  <c:v>495.72</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>526.85</c:v>
+                  <c:v>483.7</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>502.86</c:v>
+                  <c:v>487.91</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>460.56</c:v>
+                  <c:v>473.6</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>397.61</c:v>
+                  <c:v>424.19</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>399.99</c:v>
+                  <c:v>415.9</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>402.51</c:v>
+                  <c:v>408.74</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>391.88</c:v>
+                  <c:v>389.35</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>381.65</c:v>
+                  <c:v>371.88</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>365.87</c:v>
+                  <c:v>350.35</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>349.87</c:v>
+                  <c:v>329.95</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>329.08</c:v>
+                  <c:v>306.25</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>308.07</c:v>
+                  <c:v>283.51</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>286.34</c:v>
+                  <c:v>261.11</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>256.67</c:v>
+                  <c:v>232.39</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>233.38</c:v>
+                  <c:v>210.25</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>208.45</c:v>
+                  <c:v>187.24</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>184.55</c:v>
+                  <c:v>165.62</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>160.65</c:v>
+                  <c:v>144.35</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>138.62</c:v>
+                  <c:v>124.96</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>117.75</c:v>
+                  <c:v>106.71</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>100.26</c:v>
+                  <c:v>91.54</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>26.1</c:v>
+                  <c:v>19.59</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>23.34</c:v>
+                  <c:v>19.63</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>20.5</c:v>
+                  <c:v>19.3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>17.92</c:v>
+                  <c:v>18.89</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>15.36</c:v>
+                  <c:v>18.13</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>12.98</c:v>
+                  <c:v>17.16</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>10.85</c:v>
+                  <c:v>16.07</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>9</c:v>
+                  <c:v>14.91</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>6.81</c:v>
+                  <c:v>12.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4342,7 +4351,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Test_Initdis!$B$129:$B$129</c:f>
+              <c:f>Test_Initdis!$B$130:$B$130</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4394,353 +4403,353 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
+              <c:f>Test_Initdis!$D$131:$BE$131</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="54"/>
+                <c:pt idx="0">
+                  <c:v>10.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22.9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>24.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>26.4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>28.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>32.8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>35.2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>37.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>40.7</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>43.7</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>50.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>54.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>58.3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>62.6</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>67.3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>72.3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>77.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>83.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>89.8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>96.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>103.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>111.4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>119.7</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>128.6</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>138.2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>148.6</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>159.6</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>171.5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>184.3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>198.1</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>212.9</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>228.8</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>245.8</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>264.2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>283.9</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>305.1</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>327.8</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>352.3</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>378.6</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>406.8</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>437.1</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>469.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
               <c:f>Test_Initdis!$D$130:$BE$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
                 <c:pt idx="0">
-                  <c:v>10.4</c:v>
+                  <c:v>127.807058823529</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.1</c:v>
+                  <c:v>214.207058823529</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>282.12</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.9</c:v>
+                  <c:v>349.644705882353</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13.8</c:v>
+                  <c:v>503.830588235294</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.9</c:v>
+                  <c:v>582.847058823529</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16</c:v>
+                  <c:v>699.670588235294</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>17.2</c:v>
+                  <c:v>741.529411764706</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>18.4</c:v>
+                  <c:v>881.484705882353</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.8</c:v>
+                  <c:v>242.214</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21.3</c:v>
+                  <c:v>276.794</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>22.9</c:v>
+                  <c:v>311.71</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>24.6</c:v>
+                  <c:v>346.164</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>26.4</c:v>
+                  <c:v>399.252</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>28.4</c:v>
+                  <c:v>431.368</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>30.5</c:v>
+                  <c:v>481.026</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>32.8</c:v>
+                  <c:v>506.128</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>35.2</c:v>
+                  <c:v>568.456</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>37.9</c:v>
+                  <c:v>582.484</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>40.7</c:v>
+                  <c:v>610.834</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>43.7</c:v>
+                  <c:v>651.294</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>47</c:v>
+                  <c:v>662.396</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>50.5</c:v>
+                  <c:v>665.182</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>54.2</c:v>
+                  <c:v>694.008</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>58.3</c:v>
+                  <c:v>677.18</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>62.6</c:v>
+                  <c:v>683.074</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>67.3</c:v>
+                  <c:v>663.04</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>72.3</c:v>
+                  <c:v>522.08</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>77.7</c:v>
+                  <c:v>511.876923076923</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>83.5</c:v>
+                  <c:v>503.064615384615</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>89.8</c:v>
+                  <c:v>479.2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>96.5</c:v>
+                  <c:v>457.698461538462</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>103.7</c:v>
+                  <c:v>431.2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>111.4</c:v>
+                  <c:v>406.092307692308</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>119.7</c:v>
+                  <c:v>376.923076923077</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>128.6</c:v>
+                  <c:v>348.935384615385</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>138.2</c:v>
+                  <c:v>321.366153846154</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>148.6</c:v>
+                  <c:v>286.018461538462</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>159.6</c:v>
+                  <c:v>258.769230769231</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>171.5</c:v>
+                  <c:v>230.449230769231</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>184.3</c:v>
+                  <c:v>203.84</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>198.1</c:v>
+                  <c:v>177.661538461538</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>212.9</c:v>
+                  <c:v>153.796923076923</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>228.8</c:v>
+                  <c:v>131.335384615385</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>245.8</c:v>
+                  <c:v>112.664615384615</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>264.2</c:v>
+                  <c:v>19.59</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>283.9</c:v>
+                  <c:v>19.63</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>305.1</c:v>
+                  <c:v>19.3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>327.8</c:v>
+                  <c:v>18.89</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>352.3</c:v>
+                  <c:v>18.13</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>378.6</c:v>
+                  <c:v>17.16</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>406.8</c:v>
+                  <c:v>16.07</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>437.1</c:v>
+                  <c:v>14.91</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>469.8</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Test_Initdis!$D$129:$BE$129</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
-                <c:pt idx="0">
-                  <c:v>478.024</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>636.112</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>642.008</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>627.68</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>731.168</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>670.712</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>655.248</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>655.248</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>568.64</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>347.56</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>386.2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>422.21</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>454.45</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>507.34</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>528.94</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>568.58</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>575.19</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>620.67</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>608.71</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>610.75</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>621.99</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>602.39</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>575.34</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>570.31</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>526.85</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>502.86</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>460.56</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>530.146666666667</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>533.32</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>536.68</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>522.506666666667</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>508.866666666667</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>487.826666666667</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>466.493333333333</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>438.773333333333</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>410.76</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>381.786666666667</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>342.226666666667</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>311.173333333333</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>277.933333333333</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>246.066666666667</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>214.2</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>184.826666666667</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>157</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>133.68</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>30.1153846153846</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>26.9307692307692</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>23.6538461538462</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>20.6769230769231</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>17.7230769230769</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>14.9769230769231</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>12.5192307692308</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>10.3846153846154</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>7.85769230769231</c:v>
+                  <c:v>12.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="10811535"/>
-        <c:axId val="54000276"/>
+        <c:axId val="50036387"/>
+        <c:axId val="12196054"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="10811535"/>
+        <c:axId val="50036387"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -4777,8 +4786,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.602687307040049"/>
-              <c:y val="0.920520842140864"/>
+              <c:x val="0.602661100965301"/>
+              <c:y val="0.920429561982073"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -4815,12 +4824,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54000276"/>
+        <c:crossAx val="12196054"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="54000276"/>
+        <c:axId val="12196054"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -4897,7 +4906,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10811535"/>
+        <c:crossAx val="50036387"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4953,7 +4962,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart90.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -4999,10 +5008,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0696122860020141"/>
-          <c:y val="0.213320104179586"/>
-          <c:w val="0.717522658610272"/>
-          <c:h val="0.67853156393402"/>
+          <c:x val="0.0696079048398263"/>
+          <c:y val="0.213346564128008"/>
+          <c:w val="0.717477500157342"/>
+          <c:h val="0.678491689407095"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -5062,7 +5071,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$17:$U$17</c:f>
+              <c:f>Test_Initdis!$D$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
@@ -5125,7 +5134,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Test_Initdis!$D$15:$U$15</c:f>
+              <c:f>Test_Initdis!$D$16:$U$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
@@ -5193,7 +5202,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Test_Initdis!$B$16:$B$16</c:f>
+              <c:f>Test_Initdis!$B$17:$B$17</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5245,137 +5254,137 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
+              <c:f>Test_Initdis!$D$18:$U$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>19.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>35.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>37.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40.7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>43.7</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>50.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>54.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>58.3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>62.6</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>67.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
               <c:f>Test_Initdis!$D$17:$U$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>19.8</c:v>
+                  <c:v>173.01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.3</c:v>
+                  <c:v>197.71</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>22.9</c:v>
+                  <c:v>222.65</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24.6</c:v>
+                  <c:v>247.26</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>26.4</c:v>
+                  <c:v>285.18</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>28.4</c:v>
+                  <c:v>308.12</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>30.5</c:v>
+                  <c:v>343.59</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>32.8</c:v>
+                  <c:v>361.52</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>35.2</c:v>
+                  <c:v>406.04</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>37.9</c:v>
+                  <c:v>416.06</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>40.7</c:v>
+                  <c:v>436.31</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>43.7</c:v>
+                  <c:v>465.21</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>47</c:v>
+                  <c:v>473.14</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>50.5</c:v>
+                  <c:v>475.13</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>54.2</c:v>
+                  <c:v>495.72</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>58.3</c:v>
+                  <c:v>483.7</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>62.6</c:v>
+                  <c:v>487.91</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>67.3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Test_Initdis!$D$16:$U$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>347.56</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>386.2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>422.21</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>454.45</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>507.34</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>528.94</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>568.58</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>575.19</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>620.67</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>608.71</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>610.75</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>621.99</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>602.39</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>575.34</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>570.31</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>526.85</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>502.86</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>460.56</c:v>
+                  <c:v>473.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="86668558"/>
-        <c:axId val="65213519"/>
+        <c:axId val="65949989"/>
+        <c:axId val="9533278"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="86668558"/>
+        <c:axId val="65949989"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5407,12 +5416,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65213519"/>
+        <c:crossAx val="9533278"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="65213519"/>
+        <c:axId val="9533278"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5454,7 +5463,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86668558"/>
+        <c:crossAx val="65949989"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5516,14 +5525,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>661680</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>98640</xdr:rowOff>
+      <xdr:colOff>593640</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>98280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5531,8 +5540,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="10668960"/>
-        <a:ext cx="5719320" cy="2902320"/>
+        <a:off x="0" y="10870200"/>
+        <a:ext cx="5719680" cy="2901960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5546,14 +5555,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>58320</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>43560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>56160</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>2520</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>720720</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>2160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5561,8 +5570,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="58320" y="16846200"/>
-        <a:ext cx="5788080" cy="2938320"/>
+        <a:off x="58320" y="17047440"/>
+        <a:ext cx="5788440" cy="2937960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5576,14 +5585,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>59400</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>36720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>85680</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>71280</xdr:rowOff>
+      <xdr:colOff>17280</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>70920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5591,8 +5600,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="59400" y="19994040"/>
-        <a:ext cx="5816520" cy="3013920"/>
+        <a:off x="59400" y="20195280"/>
+        <a:ext cx="5816880" cy="3013560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5606,13 +5615,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>19440</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>44640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>365760</xdr:colOff>
-      <xdr:row>159</xdr:row>
+      <xdr:colOff>297720</xdr:colOff>
+      <xdr:row>160</xdr:row>
       <xdr:rowOff>27000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -5621,8 +5630,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="19440" y="24714720"/>
-        <a:ext cx="8335080" cy="4714560"/>
+        <a:off x="19440" y="24916320"/>
+        <a:ext cx="8335440" cy="4714200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5636,14 +5645,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>138600</xdr:colOff>
-      <xdr:row>160</xdr:row>
+      <xdr:row>161</xdr:row>
       <xdr:rowOff>82080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>428400</xdr:colOff>
-      <xdr:row>184</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:colOff>360360</xdr:colOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>132840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5651,8 +5660,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="138600" y="29659680"/>
-        <a:ext cx="8278560" cy="4257360"/>
+        <a:off x="138600" y="29860920"/>
+        <a:ext cx="8278920" cy="4257000"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5666,14 +5675,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>10440</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>9360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>672120</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>107640</xdr:rowOff>
+      <xdr:colOff>604080</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5681,8 +5690,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10440" y="13832640"/>
-        <a:ext cx="5719320" cy="2902320"/>
+        <a:off x="10440" y="14033880"/>
+        <a:ext cx="5719680" cy="2901960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5701,7 +5710,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:BE24"/>
-  <sheetFormatPr defaultColWidth="8.78515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.6"/>
@@ -6448,7 +6457,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.68"/>
   </cols>
@@ -6596,472 +6605,441 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BE131"/>
-  <sheetFormatPr defaultColWidth="8.78515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BE132"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="0" width="10.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="12" style="0" width="9.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="17" style="0" width="9.32"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="6" t="s">
         <v>48</v>
       </c>
-    </row>
+      <c r="C1" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>525.693494042009</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>652.932869380076</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>715.618226939296</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>708.790836222811</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>664.905286507232</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>635.182739428508</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>607.862157841551</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>626.611988345819</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>796.247155746377</v>
+      <c r="B3" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="9" t="n">
-        <f aca="false">FILLDN!D2</f>
-        <v>597.53</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <f aca="false">FILLDN!D3</f>
-        <v>795.14</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <f aca="false">FILLDN!D4</f>
-        <v>802.51</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <f aca="false">FILLDN!D5</f>
-        <v>784.6</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <f aca="false">FILLDN!D6</f>
-        <v>913.96</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <f aca="false">FILLDN!D7</f>
-        <v>838.39</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <f aca="false">FILLDN!D8</f>
-        <v>819.06</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <f aca="false">FILLDN!D8</f>
-        <v>819.06</v>
-      </c>
-      <c r="L4" s="9" t="n">
-        <f aca="false">FILLDN!D9</f>
-        <v>710.8</v>
+      <c r="D4" s="3" t="n">
+        <v>525.693494042009</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>652.932869380076</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>715.618226939296</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>708.790836222811</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>664.905286507232</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>635.182739428508</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>607.862157841551</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>626.611988345819</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>796.247155746377</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>181.06</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>303.46</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>399.67</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>495.33</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>713.76</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>825.7</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>991.2</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>1050.5</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>1248.77</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C6" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D6" s="0" t="n">
         <v>10.4</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E6" s="0" t="n">
         <v>11.1</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F6" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G6" s="0" t="n">
         <v>12.9</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H6" s="0" t="n">
         <v>13.8</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I6" s="0" t="n">
         <v>14.9</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="J6" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K6" s="0" t="n">
         <v>17.2</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L6" s="0" t="n">
         <v>18.4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2"/>
-    </row>
     <row r="7" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>52</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="13" t="n">
-        <v>17.296</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I9" s="15"/>
-      <c r="K9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="16" t="n">
-        <v>1.6</v>
+      <c r="C10" s="12" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>1.44</v>
-      </c>
+      <c r="G10" s="13" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I10" s="15"/>
+      <c r="K10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="12" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>15</v>
+      <c r="C11" s="16" t="n">
+        <v>1.6</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="13" t="n">
-        <v>23.539</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <f aca="false">G11</f>
-        <v>23.539</v>
+      <c r="G11" s="17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6"/>
-      <c r="C12" s="12"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="18"/>
+      <c r="B12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>100.041</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>50.02</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <f aca="false">G12</f>
+        <v>50.02</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6"/>
+      <c r="B13" s="18" t="s">
+        <v>64</v>
+      </c>
       <c r="C13" s="12"/>
       <c r="F13" s="6"/>
       <c r="G13" s="12"/>
       <c r="H13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="B14" s="6"/>
       <c r="C14" s="12"/>
       <c r="F14" s="6"/>
       <c r="G14" s="12"/>
       <c r="H14" s="18"/>
     </row>
     <row r="15" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>792.82374779818</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>710.200339376965</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>660.782695119878</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>640.835560877071</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>578.910091787022</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>542.262350746067</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>525.438150187442</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>539.910461957901</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>561.046691807722</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>564.35634672652</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>592.318412654218</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>619.902142675285</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>648.953116200058</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>691.681122728953</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>695.561396639587</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>676.139892021799</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>658.318402728287</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>655.589257212674</v>
-      </c>
+      <c r="B15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">FILLDN!D11</f>
-        <v>347.56</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <f aca="false">FILLDN!D12</f>
-        <v>386.2</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <f aca="false">FILLDN!D13</f>
-        <v>422.21</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <f aca="false">FILLDN!D14</f>
-        <v>454.45</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <f aca="false">FILLDN!D15</f>
-        <v>507.34</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <f aca="false">FILLDN!D16</f>
-        <v>528.94</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <f aca="false">FILLDN!D17</f>
-        <v>568.58</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <f aca="false">FILLDN!D18</f>
-        <v>575.19</v>
-      </c>
-      <c r="L16" s="9" t="n">
-        <f aca="false">FILLDN!D19</f>
-        <v>620.67</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <f aca="false">FILLDN!D20</f>
-        <v>608.71</v>
-      </c>
-      <c r="N16" s="9" t="n">
-        <f aca="false">FILLDN!D21</f>
-        <v>610.75</v>
-      </c>
-      <c r="O16" s="9" t="n">
-        <f aca="false">FILLDN!D22</f>
-        <v>621.99</v>
-      </c>
-      <c r="P16" s="9" t="n">
-        <f aca="false">FILLDN!D23</f>
-        <v>602.39</v>
-      </c>
-      <c r="Q16" s="9" t="n">
-        <f aca="false">FILLDN!D24</f>
-        <v>575.34</v>
-      </c>
-      <c r="R16" s="9" t="n">
-        <f aca="false">FILLDN!D25</f>
-        <v>570.31</v>
-      </c>
-      <c r="S16" s="9" t="n">
-        <f aca="false">FILLDN!D26</f>
-        <v>526.85</v>
-      </c>
-      <c r="T16" s="9" t="n">
-        <f aca="false">FILLDN!D27</f>
-        <v>502.86</v>
-      </c>
-      <c r="U16" s="9" t="n">
-        <f aca="false">FILLDN!D28</f>
-        <v>460.56</v>
+      <c r="D16" s="3" t="n">
+        <v>792.82374779818</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>710.200339376965</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>660.782695119878</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>640.835560877071</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>578.910091787022</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>542.262350746067</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>525.438150187442</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>539.910461957901</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>561.046691807722</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>564.35634672652</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>592.318412654218</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>619.902142675285</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>648.953116200058</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>691.681122728953</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>695.561396639587</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>676.139892021799</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>658.318402728287</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>655.589257212674</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>173.01</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>197.71</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>222.65</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>247.26</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>285.18</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>308.12</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>343.59</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>361.52</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>406.04</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>416.06</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>436.31</v>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>465.21</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>473.14</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>475.13</v>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>495.72</v>
+      </c>
+      <c r="S17" s="9" t="n">
+        <v>483.7</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>487.91</v>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>473.6</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C18" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D18" s="0" t="n">
         <v>19.8</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E18" s="0" t="n">
         <v>21.3</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F18" s="0" t="n">
         <v>22.9</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G18" s="0" t="n">
         <v>24.6</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H18" s="0" t="n">
         <v>26.4</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I18" s="0" t="n">
         <v>28.4</v>
       </c>
-      <c r="J17" s="0" t="n">
+      <c r="J18" s="0" t="n">
         <v>30.5</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K18" s="0" t="n">
         <v>32.8</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L18" s="0" t="n">
         <v>35.2</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M18" s="0" t="n">
         <v>37.9</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N18" s="0" t="n">
         <v>40.7</v>
       </c>
-      <c r="O17" s="0" t="n">
+      <c r="O18" s="0" t="n">
         <v>43.7</v>
       </c>
-      <c r="P17" s="10" t="n">
+      <c r="P18" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="Q17" s="0" t="n">
+      <c r="Q18" s="0" t="n">
         <v>50.5</v>
       </c>
-      <c r="R17" s="0" t="n">
+      <c r="R18" s="0" t="n">
         <v>54.2</v>
       </c>
-      <c r="S17" s="0" t="n">
+      <c r="S18" s="0" t="n">
         <v>58.3</v>
       </c>
-      <c r="T17" s="0" t="n">
+      <c r="T18" s="0" t="n">
         <v>62.6</v>
       </c>
-      <c r="U17" s="0" t="n">
+      <c r="U18" s="0" t="n">
         <v>67.3</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2"/>
-      <c r="C18" s="12"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="18"/>
-    </row>
     <row r="19" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>52</v>
-      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="12"/>
       <c r="F19" s="6"/>
       <c r="G19" s="12"/>
       <c r="H19" s="18"/>
@@ -7070,1648 +7048,1635 @@
       <c r="B20" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="7" t="n">
         <v>1400</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H20" s="11" t="s">
-        <v>55</v>
-      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="H21" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="13" t="n">
-        <v>19.998</v>
-      </c>
-      <c r="H21" s="19" t="n">
-        <v>94</v>
-      </c>
-      <c r="I21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="16" t="n">
-        <v>1.8</v>
+      <c r="C22" s="12" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>5</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G22" s="17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H22" s="17" t="n">
-        <v>1.903</v>
-      </c>
+      <c r="G22" s="13" t="n">
+        <v>94.22</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>160</v>
+      </c>
+      <c r="I22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="6" t="n">
-        <v>2192.5</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>15</v>
+      <c r="C23" s="16" t="n">
+        <v>1.8</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="13" t="n">
-        <v>1754.003</v>
-      </c>
-      <c r="H23" s="13" t="n">
-        <f aca="false">G23</f>
-        <v>1754.003</v>
+      <c r="G23" s="17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>2.058</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="s">
+      <c r="B24" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>18270.861</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
+      <c r="G24" s="13" t="n">
+        <v>5481.288</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <f aca="false">G24</f>
+        <v>5481.288</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>641.058893787085</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>624.781872068927</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>579.412152859297</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>526.442922432224</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>455.491548145149</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>384.571955470685</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>325.824979460309</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>279.867488619622</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>232.348668866477</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>188.745198190073</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>158.390614233429</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>131.290538897508</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>110.232084054637</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>88.6839908399312</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>76.2965180641972</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>63.2112296205677</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>52.714619449158</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>42.7530935415718</v>
+      <c r="B27" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="9" t="n">
-        <f aca="false">FILLDN!D29</f>
-        <v>397.61</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <f aca="false">FILLDN!D30</f>
-        <v>399.99</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <f aca="false">FILLDN!D31</f>
-        <v>402.51</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <f aca="false">FILLDN!D32</f>
-        <v>391.88</v>
-      </c>
-      <c r="H28" s="9" t="n">
-        <f aca="false">FILLDN!D33</f>
-        <v>381.65</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <f aca="false">FILLDN!D34</f>
-        <v>365.87</v>
-      </c>
-      <c r="J28" s="9" t="n">
-        <f aca="false">FILLDN!D35</f>
-        <v>349.87</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <f aca="false">FILLDN!D36</f>
-        <v>329.08</v>
-      </c>
-      <c r="L28" s="9" t="n">
-        <f aca="false">FILLDN!D37</f>
-        <v>308.07</v>
-      </c>
-      <c r="M28" s="9" t="n">
-        <f aca="false">FILLDN!D38</f>
-        <v>286.34</v>
-      </c>
-      <c r="N28" s="9" t="n">
-        <f aca="false">FILLDN!D39</f>
-        <v>256.67</v>
-      </c>
-      <c r="O28" s="9" t="n">
-        <f aca="false">FILLDN!D40</f>
-        <v>233.38</v>
-      </c>
-      <c r="P28" s="9" t="n">
-        <f aca="false">FILLDN!D41</f>
-        <v>208.45</v>
-      </c>
-      <c r="Q28" s="9" t="n">
-        <f aca="false">FILLDN!D42</f>
-        <v>184.55</v>
-      </c>
-      <c r="R28" s="9" t="n">
-        <f aca="false">FILLDN!D43</f>
-        <v>160.65</v>
-      </c>
-      <c r="S28" s="9" t="n">
-        <f aca="false">FILLDN!D44</f>
-        <v>138.62</v>
-      </c>
-      <c r="T28" s="9" t="n">
-        <f aca="false">FILLDN!D45</f>
-        <v>117.75</v>
-      </c>
-      <c r="U28" s="9" t="n">
-        <f aca="false">FILLDN!D46</f>
-        <v>100.26</v>
+      <c r="D28" s="3" t="n">
+        <v>641.058893787085</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>624.781872068927</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>579.412152859297</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>526.442922432224</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>455.491548145149</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>384.571955470685</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>325.824979460309</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>279.867488619622</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>232.348668866477</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>188.745198190073</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>158.390614233429</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>131.290538897508</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>110.232084054637</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>88.6839908399312</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>76.2965180641972</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>63.2112296205677</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>52.714619449158</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>42.7530935415718</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>424.19</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>415.9</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>408.74</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>371.88</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>329.95</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>283.51</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>261.11</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>232.39</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>210.25</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>187.24</v>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>165.62</v>
+      </c>
+      <c r="R29" s="9" t="n">
+        <v>144.35</v>
+      </c>
+      <c r="S29" s="9" t="n">
+        <v>124.96</v>
+      </c>
+      <c r="T29" s="9" t="n">
+        <v>106.71</v>
+      </c>
+      <c r="U29" s="9" t="n">
+        <v>91.54</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C30" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D30" s="0" t="n">
         <v>72.3</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E30" s="0" t="n">
         <v>77.7</v>
       </c>
-      <c r="F29" s="0" t="n">
+      <c r="F30" s="0" t="n">
         <v>83.5</v>
       </c>
-      <c r="G29" s="0" t="n">
+      <c r="G30" s="0" t="n">
         <v>89.8</v>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H30" s="0" t="n">
         <v>96.5</v>
       </c>
-      <c r="I29" s="0" t="n">
+      <c r="I30" s="0" t="n">
         <v>103.7</v>
       </c>
-      <c r="J29" s="0" t="n">
+      <c r="J30" s="0" t="n">
         <v>111.4</v>
       </c>
-      <c r="K29" s="0" t="n">
+      <c r="K30" s="0" t="n">
         <v>119.7</v>
       </c>
-      <c r="L29" s="0" t="n">
+      <c r="L30" s="0" t="n">
         <v>128.6</v>
       </c>
-      <c r="M29" s="0" t="n">
+      <c r="M30" s="0" t="n">
         <v>138.2</v>
       </c>
-      <c r="N29" s="0" t="n">
+      <c r="N30" s="0" t="n">
         <v>148.6</v>
       </c>
-      <c r="O29" s="0" t="n">
+      <c r="O30" s="0" t="n">
         <v>159.6</v>
       </c>
-      <c r="P29" s="0" t="n">
+      <c r="P30" s="0" t="n">
         <v>171.5</v>
       </c>
-      <c r="Q29" s="0" t="n">
+      <c r="Q30" s="0" t="n">
         <v>184.3</v>
       </c>
-      <c r="R29" s="0" t="n">
+      <c r="R30" s="0" t="n">
         <v>198.1</v>
       </c>
-      <c r="S29" s="0" t="n">
+      <c r="S30" s="0" t="n">
         <v>212.9</v>
       </c>
-      <c r="T29" s="0" t="n">
+      <c r="T30" s="0" t="n">
         <v>228.8</v>
       </c>
-      <c r="U29" s="0" t="n">
+      <c r="U30" s="0" t="n">
         <v>245.8</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="2"/>
-    </row>
     <row r="31" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>52</v>
-      </c>
+      <c r="B31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="1" t="s">
+      <c r="H33" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G33" s="13" t="n">
-        <v>319.54</v>
-      </c>
-      <c r="H33" s="19" t="n">
-        <v>201</v>
-      </c>
-      <c r="I33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="16" t="n">
-        <v>1.55</v>
+      <c r="C34" s="12" t="n">
+        <v>151.83</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>5</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H34" s="17" t="n">
-        <v>1.988</v>
-      </c>
+      <c r="G34" s="13" t="n">
+        <v>228.589</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>206</v>
+      </c>
+      <c r="I34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="7" t="n">
-        <v>21740</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>15</v>
+      <c r="C35" s="16" t="n">
+        <v>1.55</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G35" s="20" t="n">
-        <v>10652.56</v>
-      </c>
-      <c r="H35" s="20" t="n">
-        <f aca="false">G35</f>
-        <v>10652.56</v>
+      <c r="G35" s="17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>2.145</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
+      <c r="B36" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>36233.148</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G36" s="20" t="n">
+        <v>10869.945</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <f aca="false">G36</f>
+        <v>10869.945</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>33.0445745656922</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>25.9386931701922</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>20.7252269343757</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>13.991979383972</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>10.448096587855</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>7.83667466984971</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>5.73406371009997</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>4.27247490502101</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>3.36762939250147</v>
+      <c r="B39" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D40" s="9" t="n">
-        <f aca="false">FILLDN!D47</f>
-        <v>26.1</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <f aca="false">FILLDN!D48</f>
-        <v>23.34</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <f aca="false">FILLDN!D49</f>
-        <v>20.5</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <f aca="false">FILLDN!D50</f>
-        <v>17.92</v>
-      </c>
-      <c r="H40" s="9" t="n">
-        <f aca="false">FILLDN!D51</f>
-        <v>15.36</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <f aca="false">FILLDN!D52</f>
-        <v>12.98</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <f aca="false">FILLDN!D53</f>
-        <v>10.85</v>
-      </c>
-      <c r="K40" s="9" t="n">
-        <f aca="false">FILLDN!D54</f>
-        <v>9</v>
-      </c>
-      <c r="L40" s="9" t="n">
-        <f aca="false">FILLDN!D55</f>
-        <v>6.81</v>
+      <c r="D40" s="3" t="n">
+        <v>33.0445745656922</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>25.9386931701922</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>20.7252269343757</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>13.991979383972</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>10.448096587855</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>7.83667466984971</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>5.73406371009997</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>4.27247490502101</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>3.36762939250147</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>18.89</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="L41" s="9" t="n">
+        <v>12.65</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C42" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="0" t="n">
+      <c r="D42" s="0" t="n">
         <v>264.2</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E42" s="0" t="n">
         <v>283.9</v>
       </c>
-      <c r="F41" s="0" t="n">
+      <c r="F42" s="0" t="n">
         <v>305.1</v>
       </c>
-      <c r="G41" s="0" t="n">
+      <c r="G42" s="0" t="n">
         <v>327.8</v>
       </c>
-      <c r="H41" s="0" t="n">
+      <c r="H42" s="0" t="n">
         <v>352.3</v>
       </c>
-      <c r="I41" s="0" t="n">
+      <c r="I42" s="0" t="n">
         <v>378.6</v>
       </c>
-      <c r="J41" s="0" t="n">
+      <c r="J42" s="0" t="n">
         <v>406.8</v>
       </c>
-      <c r="K41" s="0" t="n">
+      <c r="K42" s="0" t="n">
         <v>437.1</v>
       </c>
-      <c r="L41" s="0" t="n">
+      <c r="L42" s="0" t="n">
         <v>469.8</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-    </row>
     <row r="43" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>52</v>
-      </c>
+      <c r="B43" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="F44" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C45" s="6" t="n">
-        <v>340</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="1" t="s">
+      <c r="H45" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G45" s="13" t="n">
-        <v>324</v>
-      </c>
-      <c r="H45" s="19" t="n">
-        <v>324</v>
-      </c>
-      <c r="I45" s="15"/>
     </row>
     <row r="46" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="16" t="n">
-        <v>1.55</v>
+      <c r="C46" s="6" t="n">
+        <v>340</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>5</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G46" s="17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H46" s="1" t="n">
-        <v>1.87</v>
-      </c>
+      <c r="G46" s="13" t="n">
+        <v>324</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I46" s="15"/>
     </row>
     <row r="47" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="12" t="n">
-        <v>9927.8</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>15</v>
+      <c r="C47" s="16" t="n">
+        <v>1.55</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G47" s="13" t="n">
-        <v>4467.495</v>
-      </c>
-      <c r="H47" s="13" t="n">
-        <f aca="false">G47</f>
-        <v>4467.495</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-    </row>
+      <c r="G47" s="17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>46329.574</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>13898.873</v>
+      </c>
+      <c r="H48" s="20" t="n">
+        <f aca="false">G48</f>
+        <v>13898.873</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>68</v>
-      </c>
+      <c r="A50" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
-      <c r="H50" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="I50" s="0" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="51" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B51" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="0" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="I51" s="0" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
+      <c r="A52" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="C52" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="0" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="I52" s="0" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M78" s="21"/>
-    </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M80" s="21"/>
-    </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="T100" s="3"/>
-      <c r="U100" s="3"/>
-      <c r="V100" s="3"/>
-    </row>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="T102" s="10"/>
-      <c r="U102" s="10"/>
-    </row>
-    <row r="126" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B126" s="0" t="s">
+    <row r="53" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D126" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F126" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G126" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="H126" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="I126" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="J126" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="K126" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="L126" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="M126" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="N126" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="O126" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="P126" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q126" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="R126" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="S126" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="T126" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="U126" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="V126" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="W126" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="X126" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y126" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z126" s="0" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA126" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB126" s="0" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC126" s="0" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD126" s="0" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE126" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF126" s="0" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG126" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH126" s="0" t="n">
-        <v>31</v>
-      </c>
-      <c r="AI126" s="0" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ126" s="0" t="n">
-        <v>33</v>
-      </c>
-      <c r="AK126" s="0" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL126" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AM126" s="0" t="n">
-        <v>36</v>
-      </c>
-      <c r="AN126" s="0" t="n">
-        <v>37</v>
-      </c>
-      <c r="AO126" s="0" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP126" s="0" t="n">
-        <v>39</v>
-      </c>
-      <c r="AQ126" s="0" t="n">
-        <v>40</v>
-      </c>
-      <c r="AR126" s="0" t="n">
-        <v>41</v>
-      </c>
-      <c r="AS126" s="0" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT126" s="0" t="n">
-        <v>43</v>
-      </c>
-      <c r="AU126" s="0" t="n">
-        <v>44</v>
-      </c>
-      <c r="AV126" s="0" t="n">
-        <v>45</v>
-      </c>
-      <c r="AW126" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX126" s="0" t="n">
-        <v>47</v>
-      </c>
-      <c r="AY126" s="0" t="n">
-        <v>48</v>
-      </c>
-      <c r="AZ126" s="0" t="n">
-        <v>49</v>
-      </c>
-      <c r="BA126" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB126" s="0" t="n">
-        <v>51</v>
-      </c>
-      <c r="BC126" s="0" t="n">
-        <v>52</v>
-      </c>
-      <c r="BD126" s="0" t="n">
-        <v>53</v>
-      </c>
-      <c r="BE126" s="0" t="n">
-        <v>54</v>
-      </c>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="I53" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M79" s="21"/>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M81" s="21"/>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T101" s="3"/>
+      <c r="U101" s="3"/>
+      <c r="V101" s="3"/>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T103" s="10"/>
+      <c r="U103" s="10"/>
     </row>
     <row r="127" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B127" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D127" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G127" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I127" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J127" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="K127" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="L127" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="M127" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="N127" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="O127" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="P127" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q127" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="R127" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="S127" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="T127" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="U127" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="V127" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="W127" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="X127" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y127" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z127" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA127" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB127" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC127" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD127" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE127" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF127" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG127" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH127" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="AI127" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ127" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="AK127" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL127" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AM127" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN127" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO127" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP127" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="AQ127" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR127" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="AS127" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT127" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="AU127" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="AV127" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="AW127" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX127" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="AY127" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ127" s="0" t="n">
         <v>49</v>
       </c>
-      <c r="C127" s="0" t="s">
+      <c r="BA127" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB127" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="BC127" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="BD127" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE127" s="0" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B128" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C128" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D127" s="3" t="n">
+      <c r="D128" s="3" t="n">
         <v>525.693494042009</v>
       </c>
-      <c r="E127" s="3" t="n">
+      <c r="E128" s="3" t="n">
         <v>652.932869380076</v>
       </c>
-      <c r="F127" s="3" t="n">
+      <c r="F128" s="3" t="n">
         <v>715.618226939296</v>
       </c>
-      <c r="G127" s="3" t="n">
+      <c r="G128" s="3" t="n">
         <v>708.790836222811</v>
       </c>
-      <c r="H127" s="3" t="n">
+      <c r="H128" s="3" t="n">
         <v>664.905286507232</v>
       </c>
-      <c r="I127" s="3" t="n">
+      <c r="I128" s="3" t="n">
         <v>635.182739428508</v>
       </c>
-      <c r="J127" s="3" t="n">
+      <c r="J128" s="3" t="n">
         <v>607.862157841551</v>
       </c>
-      <c r="K127" s="3" t="n">
+      <c r="K128" s="3" t="n">
         <v>626.611988345819</v>
       </c>
-      <c r="L127" s="3" t="n">
+      <c r="L128" s="3" t="n">
         <v>796.247155746377</v>
       </c>
-      <c r="M127" s="3" t="n">
+      <c r="M128" s="3" t="n">
         <v>792.82374779818</v>
       </c>
-      <c r="N127" s="3" t="n">
+      <c r="N128" s="3" t="n">
         <v>710.200339376965</v>
       </c>
-      <c r="O127" s="3" t="n">
+      <c r="O128" s="3" t="n">
         <v>660.782695119878</v>
       </c>
-      <c r="P127" s="3" t="n">
+      <c r="P128" s="3" t="n">
         <v>640.835560877071</v>
       </c>
-      <c r="Q127" s="3" t="n">
+      <c r="Q128" s="3" t="n">
         <v>578.910091787022</v>
       </c>
-      <c r="R127" s="3" t="n">
+      <c r="R128" s="3" t="n">
         <v>542.262350746067</v>
       </c>
-      <c r="S127" s="3" t="n">
+      <c r="S128" s="3" t="n">
         <v>525.438150187442</v>
       </c>
-      <c r="T127" s="3" t="n">
+      <c r="T128" s="3" t="n">
         <v>539.910461957901</v>
       </c>
-      <c r="U127" s="3" t="n">
+      <c r="U128" s="3" t="n">
         <v>561.046691807722</v>
       </c>
-      <c r="V127" s="3" t="n">
+      <c r="V128" s="3" t="n">
         <v>564.35634672652</v>
       </c>
-      <c r="W127" s="3" t="n">
+      <c r="W128" s="3" t="n">
         <v>592.318412654218</v>
       </c>
-      <c r="X127" s="3" t="n">
+      <c r="X128" s="3" t="n">
         <v>619.902142675285</v>
       </c>
-      <c r="Y127" s="3" t="n">
+      <c r="Y128" s="3" t="n">
         <v>648.953116200058</v>
       </c>
-      <c r="Z127" s="3" t="n">
+      <c r="Z128" s="3" t="n">
         <v>691.681122728953</v>
       </c>
-      <c r="AA127" s="3" t="n">
+      <c r="AA128" s="3" t="n">
         <v>695.561396639587</v>
       </c>
-      <c r="AB127" s="3" t="n">
+      <c r="AB128" s="3" t="n">
         <v>676.139892021799</v>
       </c>
-      <c r="AC127" s="3" t="n">
+      <c r="AC128" s="3" t="n">
         <v>658.318402728287</v>
       </c>
-      <c r="AD127" s="3" t="n">
+      <c r="AD128" s="3" t="n">
         <v>655.589257212674</v>
       </c>
-      <c r="AE127" s="3" t="n">
+      <c r="AE128" s="3" t="n">
         <v>641.058893787085</v>
       </c>
-      <c r="AF127" s="3" t="n">
+      <c r="AF128" s="3" t="n">
         <v>624.781872068927</v>
       </c>
-      <c r="AG127" s="3" t="n">
+      <c r="AG128" s="3" t="n">
         <v>579.412152859297</v>
       </c>
-      <c r="AH127" s="3" t="n">
+      <c r="AH128" s="3" t="n">
         <v>526.442922432224</v>
       </c>
-      <c r="AI127" s="3" t="n">
+      <c r="AI128" s="3" t="n">
         <v>455.491548145149</v>
       </c>
-      <c r="AJ127" s="3" t="n">
+      <c r="AJ128" s="3" t="n">
         <v>384.571955470685</v>
       </c>
-      <c r="AK127" s="3" t="n">
+      <c r="AK128" s="3" t="n">
         <v>325.824979460309</v>
       </c>
-      <c r="AL127" s="3" t="n">
+      <c r="AL128" s="3" t="n">
         <v>279.867488619622</v>
       </c>
-      <c r="AM127" s="3" t="n">
+      <c r="AM128" s="3" t="n">
         <v>232.348668866477</v>
       </c>
-      <c r="AN127" s="3" t="n">
+      <c r="AN128" s="3" t="n">
         <v>188.745198190073</v>
       </c>
-      <c r="AO127" s="3" t="n">
+      <c r="AO128" s="3" t="n">
         <v>158.390614233429</v>
       </c>
-      <c r="AP127" s="3" t="n">
+      <c r="AP128" s="3" t="n">
         <v>131.290538897508</v>
       </c>
-      <c r="AQ127" s="3" t="n">
+      <c r="AQ128" s="3" t="n">
         <v>110.232084054637</v>
       </c>
-      <c r="AR127" s="3" t="n">
+      <c r="AR128" s="3" t="n">
         <v>88.6839908399312</v>
       </c>
-      <c r="AS127" s="3" t="n">
+      <c r="AS128" s="3" t="n">
         <v>76.2965180641972</v>
       </c>
-      <c r="AT127" s="3" t="n">
+      <c r="AT128" s="3" t="n">
         <v>63.2112296205677</v>
       </c>
-      <c r="AU127" s="3" t="n">
+      <c r="AU128" s="3" t="n">
         <v>52.714619449158</v>
       </c>
-      <c r="AV127" s="3" t="n">
+      <c r="AV128" s="3" t="n">
         <v>42.7530935415718</v>
       </c>
-      <c r="AW127" s="22" t="n">
+      <c r="AW128" s="22" t="n">
         <v>33.0445745656922</v>
       </c>
-      <c r="AX127" s="3" t="n">
+      <c r="AX128" s="3" t="n">
         <v>25.9386931701922</v>
       </c>
-      <c r="AY127" s="3" t="n">
+      <c r="AY128" s="3" t="n">
         <v>20.7252269343757</v>
       </c>
-      <c r="AZ127" s="3" t="n">
+      <c r="AZ128" s="3" t="n">
         <v>13.991979383972</v>
       </c>
-      <c r="BA127" s="3" t="n">
+      <c r="BA128" s="3" t="n">
         <v>10.448096587855</v>
       </c>
-      <c r="BB127" s="3" t="n">
+      <c r="BB128" s="3" t="n">
         <v>7.83667466984971</v>
       </c>
-      <c r="BC127" s="3" t="n">
+      <c r="BC128" s="3" t="n">
         <v>5.73406371009997</v>
       </c>
-      <c r="BD127" s="3" t="n">
+      <c r="BD128" s="3" t="n">
         <v>4.27247490502101</v>
       </c>
-      <c r="BE127" s="3" t="n">
+      <c r="BE128" s="3" t="n">
         <v>3.36762939250147</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B128" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="6" t="n">
-        <f aca="false">D4</f>
-        <v>597.53</v>
-      </c>
-      <c r="E128" s="6" t="n">
-        <f aca="false">E4</f>
-        <v>795.14</v>
-      </c>
-      <c r="F128" s="6" t="n">
-        <f aca="false">F4</f>
-        <v>802.51</v>
-      </c>
-      <c r="G128" s="6" t="n">
-        <f aca="false">G4</f>
-        <v>784.6</v>
-      </c>
-      <c r="H128" s="6" t="n">
-        <f aca="false">H4</f>
-        <v>913.96</v>
-      </c>
-      <c r="I128" s="6" t="n">
-        <f aca="false">I4</f>
-        <v>838.39</v>
-      </c>
-      <c r="J128" s="6" t="n">
-        <f aca="false">J4</f>
-        <v>819.06</v>
-      </c>
-      <c r="K128" s="6" t="n">
-        <f aca="false">K4</f>
-        <v>819.06</v>
-      </c>
-      <c r="L128" s="6" t="n">
-        <f aca="false">L4</f>
-        <v>710.8</v>
-      </c>
-      <c r="M128" s="6" t="n">
-        <f aca="false">D16</f>
-        <v>347.56</v>
-      </c>
-      <c r="N128" s="6" t="n">
-        <f aca="false">E16</f>
-        <v>386.2</v>
-      </c>
-      <c r="O128" s="6" t="n">
-        <f aca="false">F16</f>
-        <v>422.21</v>
-      </c>
-      <c r="P128" s="6" t="n">
-        <f aca="false">G16</f>
-        <v>454.45</v>
-      </c>
-      <c r="Q128" s="6" t="n">
-        <f aca="false">H16</f>
-        <v>507.34</v>
-      </c>
-      <c r="R128" s="6" t="n">
-        <f aca="false">I16</f>
-        <v>528.94</v>
-      </c>
-      <c r="S128" s="6" t="n">
-        <f aca="false">J16</f>
-        <v>568.58</v>
-      </c>
-      <c r="T128" s="6" t="n">
-        <f aca="false">K16</f>
-        <v>575.19</v>
-      </c>
-      <c r="U128" s="6" t="n">
-        <f aca="false">L16</f>
-        <v>620.67</v>
-      </c>
-      <c r="V128" s="6" t="n">
-        <f aca="false">M16</f>
-        <v>608.71</v>
-      </c>
-      <c r="W128" s="6" t="n">
-        <f aca="false">N16</f>
-        <v>610.75</v>
-      </c>
-      <c r="X128" s="6" t="n">
-        <f aca="false">O16</f>
-        <v>621.99</v>
-      </c>
-      <c r="Y128" s="6" t="n">
-        <f aca="false">P16</f>
-        <v>602.39</v>
-      </c>
-      <c r="Z128" s="6" t="n">
-        <f aca="false">Q16</f>
-        <v>575.34</v>
-      </c>
-      <c r="AA128" s="6" t="n">
-        <f aca="false">R16</f>
-        <v>570.31</v>
-      </c>
-      <c r="AB128" s="6" t="n">
-        <f aca="false">S16</f>
-        <v>526.85</v>
-      </c>
-      <c r="AC128" s="6" t="n">
-        <f aca="false">T16</f>
-        <v>502.86</v>
-      </c>
-      <c r="AD128" s="6" t="n">
-        <f aca="false">U16</f>
-        <v>460.56</v>
-      </c>
-      <c r="AE128" s="6" t="n">
-        <f aca="false">D28</f>
-        <v>397.61</v>
-      </c>
-      <c r="AF128" s="6" t="n">
-        <f aca="false">E28</f>
-        <v>399.99</v>
-      </c>
-      <c r="AG128" s="6" t="n">
-        <f aca="false">F28</f>
-        <v>402.51</v>
-      </c>
-      <c r="AH128" s="6" t="n">
-        <f aca="false">G28</f>
-        <v>391.88</v>
-      </c>
-      <c r="AI128" s="6" t="n">
-        <f aca="false">H28</f>
-        <v>381.65</v>
-      </c>
-      <c r="AJ128" s="6" t="n">
-        <f aca="false">I28</f>
-        <v>365.87</v>
-      </c>
-      <c r="AK128" s="6" t="n">
-        <f aca="false">J28</f>
-        <v>349.87</v>
-      </c>
-      <c r="AL128" s="6" t="n">
-        <f aca="false">K28</f>
-        <v>329.08</v>
-      </c>
-      <c r="AM128" s="6" t="n">
-        <f aca="false">L28</f>
-        <v>308.07</v>
-      </c>
-      <c r="AN128" s="6" t="n">
-        <f aca="false">M28</f>
-        <v>286.34</v>
-      </c>
-      <c r="AO128" s="6" t="n">
-        <f aca="false">N28</f>
-        <v>256.67</v>
-      </c>
-      <c r="AP128" s="6" t="n">
-        <f aca="false">O28</f>
-        <v>233.38</v>
-      </c>
-      <c r="AQ128" s="6" t="n">
-        <f aca="false">P28</f>
-        <v>208.45</v>
-      </c>
-      <c r="AR128" s="6" t="n">
-        <f aca="false">Q28</f>
-        <v>184.55</v>
-      </c>
-      <c r="AS128" s="6" t="n">
-        <f aca="false">R28</f>
-        <v>160.65</v>
-      </c>
-      <c r="AT128" s="6" t="n">
-        <f aca="false">S28</f>
-        <v>138.62</v>
-      </c>
-      <c r="AU128" s="6" t="n">
-        <f aca="false">T28</f>
-        <v>117.75</v>
-      </c>
-      <c r="AV128" s="6" t="n">
-        <f aca="false">U28</f>
-        <v>100.26</v>
-      </c>
-      <c r="AW128" s="1" t="n">
-        <f aca="false">D40</f>
-        <v>26.1</v>
-      </c>
-      <c r="AX128" s="6" t="n">
-        <f aca="false">E40</f>
-        <v>23.34</v>
-      </c>
-      <c r="AY128" s="6" t="n">
-        <f aca="false">F40</f>
-        <v>20.5</v>
-      </c>
-      <c r="AZ128" s="6" t="n">
-        <f aca="false">G40</f>
-        <v>17.92</v>
-      </c>
-      <c r="BA128" s="6" t="n">
-        <f aca="false">H40</f>
-        <v>15.36</v>
-      </c>
-      <c r="BB128" s="6" t="n">
-        <f aca="false">I40</f>
-        <v>12.98</v>
-      </c>
-      <c r="BC128" s="6" t="n">
-        <f aca="false">J40</f>
-        <v>10.85</v>
-      </c>
-      <c r="BD128" s="6" t="n">
-        <f aca="false">K40</f>
-        <v>9</v>
-      </c>
-      <c r="BE128" s="6" t="n">
-        <f aca="false">L40</f>
-        <v>6.81</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B129" s="6" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D129" s="12" t="n">
-        <f aca="false">D128*($C$7/$C$8)</f>
-        <v>478.024</v>
-      </c>
-      <c r="E129" s="12" t="n">
-        <f aca="false">E128*($C$7/$C$8)</f>
-        <v>636.112</v>
-      </c>
-      <c r="F129" s="12" t="n">
-        <f aca="false">F128*($C$7/$C$8)</f>
-        <v>642.008</v>
-      </c>
-      <c r="G129" s="12" t="n">
-        <f aca="false">G128*($C$7/$C$8)</f>
-        <v>627.68</v>
-      </c>
-      <c r="H129" s="12" t="n">
-        <f aca="false">H128*($C$7/$C$8)</f>
-        <v>731.168</v>
-      </c>
-      <c r="I129" s="12" t="n">
-        <f aca="false">I128*($C$7/$C$8)</f>
-        <v>670.712</v>
-      </c>
-      <c r="J129" s="12" t="n">
-        <f aca="false">J128*($C$7/$C$8)</f>
-        <v>655.248</v>
-      </c>
-      <c r="K129" s="12" t="n">
-        <f aca="false">K128*($C$7/$C$8)</f>
-        <v>655.248</v>
-      </c>
-      <c r="L129" s="12" t="n">
-        <f aca="false">L128*($C$7/$C$8)</f>
-        <v>568.64</v>
-      </c>
-      <c r="M129" s="12" t="n">
-        <f aca="false">M128*($C$19/$C$20)</f>
-        <v>347.56</v>
-      </c>
-      <c r="N129" s="12" t="n">
-        <f aca="false">N128*($C$19/$C$20)</f>
-        <v>386.2</v>
-      </c>
-      <c r="O129" s="12" t="n">
-        <f aca="false">O128*($C$19/$C$20)</f>
-        <v>422.21</v>
-      </c>
-      <c r="P129" s="12" t="n">
-        <f aca="false">P128*($C$19/$C$20)</f>
-        <v>454.45</v>
-      </c>
-      <c r="Q129" s="12" t="n">
-        <f aca="false">Q128*($C$19/$C$20)</f>
-        <v>507.34</v>
-      </c>
-      <c r="R129" s="12" t="n">
-        <f aca="false">R128*($C$19/$C$20)</f>
-        <v>528.94</v>
-      </c>
-      <c r="S129" s="12" t="n">
-        <f aca="false">S128*($C$19/$C$20)</f>
-        <v>568.58</v>
-      </c>
-      <c r="T129" s="12" t="n">
-        <f aca="false">T128*($C$19/$C$20)</f>
-        <v>575.19</v>
-      </c>
-      <c r="U129" s="12" t="n">
-        <f aca="false">U128*($C$19/$C$20)</f>
-        <v>620.67</v>
-      </c>
-      <c r="V129" s="12" t="n">
-        <f aca="false">V128*($C$19/$C$20)</f>
-        <v>608.71</v>
-      </c>
-      <c r="W129" s="12" t="n">
-        <f aca="false">W128*($C$19/$C$20)</f>
-        <v>610.75</v>
-      </c>
-      <c r="X129" s="12" t="n">
-        <f aca="false">X128*($C$19/$C$20)</f>
-        <v>621.99</v>
-      </c>
-      <c r="Y129" s="12" t="n">
-        <f aca="false">Y128*($C$19/$C$20)</f>
-        <v>602.39</v>
-      </c>
-      <c r="Z129" s="12" t="n">
-        <f aca="false">Z128*($C$19/$C$20)</f>
-        <v>575.34</v>
-      </c>
-      <c r="AA129" s="12" t="n">
-        <f aca="false">AA128*($C$19/$C$20)</f>
-        <v>570.31</v>
-      </c>
-      <c r="AB129" s="12" t="n">
-        <f aca="false">AB128*($C$19/$C$20)</f>
-        <v>526.85</v>
-      </c>
-      <c r="AC129" s="12" t="n">
-        <f aca="false">AC128*($C$19/$C$20)</f>
-        <v>502.86</v>
-      </c>
-      <c r="AD129" s="12" t="n">
-        <f aca="false">AD128*($C$19/$C$20)</f>
-        <v>460.56</v>
+      <c r="D129" s="6" t="n">
+        <f aca="false">D5</f>
+        <v>181.06</v>
+      </c>
+      <c r="E129" s="6" t="n">
+        <f aca="false">E5</f>
+        <v>303.46</v>
+      </c>
+      <c r="F129" s="6" t="n">
+        <f aca="false">F5</f>
+        <v>399.67</v>
+      </c>
+      <c r="G129" s="6" t="n">
+        <f aca="false">G5</f>
+        <v>495.33</v>
+      </c>
+      <c r="H129" s="6" t="n">
+        <f aca="false">H5</f>
+        <v>713.76</v>
+      </c>
+      <c r="I129" s="6" t="n">
+        <f aca="false">I5</f>
+        <v>825.7</v>
+      </c>
+      <c r="J129" s="6" t="n">
+        <f aca="false">J5</f>
+        <v>991.2</v>
+      </c>
+      <c r="K129" s="6" t="n">
+        <f aca="false">K5</f>
+        <v>1050.5</v>
+      </c>
+      <c r="L129" s="6" t="n">
+        <f aca="false">L5</f>
+        <v>1248.77</v>
+      </c>
+      <c r="M129" s="6" t="n">
+        <f aca="false">D17</f>
+        <v>173.01</v>
+      </c>
+      <c r="N129" s="6" t="n">
+        <f aca="false">E17</f>
+        <v>197.71</v>
+      </c>
+      <c r="O129" s="6" t="n">
+        <f aca="false">F17</f>
+        <v>222.65</v>
+      </c>
+      <c r="P129" s="6" t="n">
+        <f aca="false">G17</f>
+        <v>247.26</v>
+      </c>
+      <c r="Q129" s="6" t="n">
+        <f aca="false">H17</f>
+        <v>285.18</v>
+      </c>
+      <c r="R129" s="6" t="n">
+        <f aca="false">I17</f>
+        <v>308.12</v>
+      </c>
+      <c r="S129" s="6" t="n">
+        <f aca="false">J17</f>
+        <v>343.59</v>
+      </c>
+      <c r="T129" s="6" t="n">
+        <f aca="false">K17</f>
+        <v>361.52</v>
+      </c>
+      <c r="U129" s="6" t="n">
+        <f aca="false">L17</f>
+        <v>406.04</v>
+      </c>
+      <c r="V129" s="6" t="n">
+        <f aca="false">M17</f>
+        <v>416.06</v>
+      </c>
+      <c r="W129" s="6" t="n">
+        <f aca="false">N17</f>
+        <v>436.31</v>
+      </c>
+      <c r="X129" s="6" t="n">
+        <f aca="false">O17</f>
+        <v>465.21</v>
+      </c>
+      <c r="Y129" s="6" t="n">
+        <f aca="false">P17</f>
+        <v>473.14</v>
+      </c>
+      <c r="Z129" s="6" t="n">
+        <f aca="false">Q17</f>
+        <v>475.13</v>
+      </c>
+      <c r="AA129" s="6" t="n">
+        <f aca="false">R17</f>
+        <v>495.72</v>
+      </c>
+      <c r="AB129" s="6" t="n">
+        <f aca="false">S17</f>
+        <v>483.7</v>
+      </c>
+      <c r="AC129" s="6" t="n">
+        <f aca="false">T17</f>
+        <v>487.91</v>
+      </c>
+      <c r="AD129" s="6" t="n">
+        <f aca="false">U17</f>
+        <v>473.6</v>
       </c>
       <c r="AE129" s="6" t="n">
-        <f aca="false">AE128*($C$31/$C$32)</f>
-        <v>530.146666666667</v>
+        <f aca="false">D29</f>
+        <v>424.19</v>
       </c>
       <c r="AF129" s="6" t="n">
-        <f aca="false">AF128*($C$31/$C$32)</f>
-        <v>533.32</v>
+        <f aca="false">E29</f>
+        <v>415.9</v>
       </c>
       <c r="AG129" s="6" t="n">
-        <f aca="false">AG128*($C$31/$C$32)</f>
-        <v>536.68</v>
+        <f aca="false">F29</f>
+        <v>408.74</v>
       </c>
       <c r="AH129" s="6" t="n">
-        <f aca="false">AH128*($C$31/$C$32)</f>
-        <v>522.506666666667</v>
+        <f aca="false">G29</f>
+        <v>389.35</v>
       </c>
       <c r="AI129" s="6" t="n">
-        <f aca="false">AI128*($C$31/$C$32)</f>
-        <v>508.866666666667</v>
+        <f aca="false">H29</f>
+        <v>371.88</v>
       </c>
       <c r="AJ129" s="6" t="n">
-        <f aca="false">AJ128*($C$31/$C$32)</f>
-        <v>487.826666666667</v>
+        <f aca="false">I29</f>
+        <v>350.35</v>
       </c>
       <c r="AK129" s="6" t="n">
-        <f aca="false">AK128*($C$31/$C$32)</f>
-        <v>466.493333333333</v>
+        <f aca="false">J29</f>
+        <v>329.95</v>
       </c>
       <c r="AL129" s="6" t="n">
-        <f aca="false">AL128*($C$31/$C$32)</f>
-        <v>438.773333333333</v>
+        <f aca="false">K29</f>
+        <v>306.25</v>
       </c>
       <c r="AM129" s="6" t="n">
-        <f aca="false">AM128*($C$31/$C$32)</f>
-        <v>410.76</v>
+        <f aca="false">L29</f>
+        <v>283.51</v>
       </c>
       <c r="AN129" s="6" t="n">
-        <f aca="false">AN128*($C$31/$C$32)</f>
-        <v>381.786666666667</v>
+        <f aca="false">M29</f>
+        <v>261.11</v>
       </c>
       <c r="AO129" s="6" t="n">
-        <f aca="false">AO128*($C$31/$C$32)</f>
-        <v>342.226666666667</v>
+        <f aca="false">N29</f>
+        <v>232.39</v>
       </c>
       <c r="AP129" s="6" t="n">
-        <f aca="false">AP128*($C$31/$C$32)</f>
-        <v>311.173333333333</v>
+        <f aca="false">O29</f>
+        <v>210.25</v>
       </c>
       <c r="AQ129" s="6" t="n">
-        <f aca="false">AQ128*($C$31/$C$32)</f>
-        <v>277.933333333333</v>
+        <f aca="false">P29</f>
+        <v>187.24</v>
       </c>
       <c r="AR129" s="6" t="n">
-        <f aca="false">AR128*($C$31/$C$32)</f>
-        <v>246.066666666667</v>
+        <f aca="false">Q29</f>
+        <v>165.62</v>
       </c>
       <c r="AS129" s="6" t="n">
-        <f aca="false">AS128*($C$31/$C$32)</f>
-        <v>214.2</v>
+        <f aca="false">R29</f>
+        <v>144.35</v>
       </c>
       <c r="AT129" s="6" t="n">
-        <f aca="false">AT128*($C$31/$C$32)</f>
-        <v>184.826666666667</v>
+        <f aca="false">S29</f>
+        <v>124.96</v>
       </c>
       <c r="AU129" s="6" t="n">
-        <f aca="false">AU128*($C$31/$C$32)</f>
-        <v>157</v>
+        <f aca="false">T29</f>
+        <v>106.71</v>
       </c>
       <c r="AV129" s="6" t="n">
-        <f aca="false">AV128*($C$31/$C$32)</f>
-        <v>133.68</v>
+        <f aca="false">U29</f>
+        <v>91.54</v>
       </c>
       <c r="AW129" s="1" t="n">
-        <f aca="false">AW128*($C$43/$C$44)</f>
-        <v>30.1153846153846</v>
+        <f aca="false">D41</f>
+        <v>19.59</v>
       </c>
       <c r="AX129" s="6" t="n">
-        <f aca="false">AX128*($C$43/$C$44)</f>
-        <v>26.9307692307692</v>
+        <f aca="false">E41</f>
+        <v>19.63</v>
       </c>
       <c r="AY129" s="6" t="n">
-        <f aca="false">AY128*($C$43/$C$44)</f>
-        <v>23.6538461538462</v>
+        <f aca="false">F41</f>
+        <v>19.3</v>
       </c>
       <c r="AZ129" s="6" t="n">
-        <f aca="false">AZ128*($C$43/$C$44)</f>
-        <v>20.6769230769231</v>
+        <f aca="false">G41</f>
+        <v>18.89</v>
       </c>
       <c r="BA129" s="6" t="n">
-        <f aca="false">BA128*($C$43/$C$44)</f>
-        <v>17.7230769230769</v>
+        <f aca="false">H41</f>
+        <v>18.13</v>
       </c>
       <c r="BB129" s="6" t="n">
-        <f aca="false">BB128*($C$43/$C$44)</f>
-        <v>14.9769230769231</v>
+        <f aca="false">I41</f>
+        <v>17.16</v>
       </c>
       <c r="BC129" s="6" t="n">
-        <f aca="false">BC128*($C$43/$C$44)</f>
-        <v>12.5192307692308</v>
+        <f aca="false">J41</f>
+        <v>16.07</v>
       </c>
       <c r="BD129" s="6" t="n">
-        <f aca="false">BD128*($C$43/$C$44)</f>
-        <v>10.3846153846154</v>
+        <f aca="false">K41</f>
+        <v>14.91</v>
       </c>
       <c r="BE129" s="6" t="n">
-        <f aca="false">BE128*($C$43/$C$44)</f>
-        <v>7.85769230769231</v>
+        <f aca="false">L41</f>
+        <v>12.65</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="12" t="n">
+        <f aca="false">D129*($C$8/$C$9)</f>
+        <v>127.807058823529</v>
+      </c>
+      <c r="E130" s="12" t="n">
+        <f aca="false">E129*($C$8/$C$9)</f>
+        <v>214.207058823529</v>
+      </c>
+      <c r="F130" s="12" t="n">
+        <f aca="false">F129*($C$8/$C$9)</f>
+        <v>282.12</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <f aca="false">G129*($C$8/$C$9)</f>
+        <v>349.644705882353</v>
+      </c>
+      <c r="H130" s="12" t="n">
+        <f aca="false">H129*($C$8/$C$9)</f>
+        <v>503.830588235294</v>
+      </c>
+      <c r="I130" s="12" t="n">
+        <f aca="false">I129*($C$8/$C$9)</f>
+        <v>582.847058823529</v>
+      </c>
+      <c r="J130" s="12" t="n">
+        <f aca="false">J129*($C$8/$C$9)</f>
+        <v>699.670588235294</v>
+      </c>
+      <c r="K130" s="12" t="n">
+        <f aca="false">K129*($C$8/$C$9)</f>
+        <v>741.529411764706</v>
+      </c>
+      <c r="L130" s="12" t="n">
+        <f aca="false">L129*($C$8/$C$9)</f>
+        <v>881.484705882353</v>
+      </c>
+      <c r="M130" s="12" t="n">
+        <f aca="false">M129*($C$20/$C$21)</f>
+        <v>242.214</v>
+      </c>
+      <c r="N130" s="12" t="n">
+        <f aca="false">N129*($C$20/$C$21)</f>
+        <v>276.794</v>
+      </c>
+      <c r="O130" s="12" t="n">
+        <f aca="false">O129*($C$20/$C$21)</f>
+        <v>311.71</v>
+      </c>
+      <c r="P130" s="12" t="n">
+        <f aca="false">P129*($C$20/$C$21)</f>
+        <v>346.164</v>
+      </c>
+      <c r="Q130" s="12" t="n">
+        <f aca="false">Q129*($C$20/$C$21)</f>
+        <v>399.252</v>
+      </c>
+      <c r="R130" s="12" t="n">
+        <f aca="false">R129*($C$20/$C$21)</f>
+        <v>431.368</v>
+      </c>
+      <c r="S130" s="12" t="n">
+        <f aca="false">S129*($C$20/$C$21)</f>
+        <v>481.026</v>
+      </c>
+      <c r="T130" s="12" t="n">
+        <f aca="false">T129*($C$20/$C$21)</f>
+        <v>506.128</v>
+      </c>
+      <c r="U130" s="12" t="n">
+        <f aca="false">U129*($C$20/$C$21)</f>
+        <v>568.456</v>
+      </c>
+      <c r="V130" s="12" t="n">
+        <f aca="false">V129*($C$20/$C$21)</f>
+        <v>582.484</v>
+      </c>
+      <c r="W130" s="12" t="n">
+        <f aca="false">W129*($C$20/$C$21)</f>
+        <v>610.834</v>
+      </c>
+      <c r="X130" s="12" t="n">
+        <f aca="false">X129*($C$20/$C$21)</f>
+        <v>651.294</v>
+      </c>
+      <c r="Y130" s="12" t="n">
+        <f aca="false">Y129*($C$20/$C$21)</f>
+        <v>662.396</v>
+      </c>
+      <c r="Z130" s="12" t="n">
+        <f aca="false">Z129*($C$20/$C$21)</f>
+        <v>665.182</v>
+      </c>
+      <c r="AA130" s="12" t="n">
+        <f aca="false">AA129*($C$20/$C$21)</f>
+        <v>694.008</v>
+      </c>
+      <c r="AB130" s="12" t="n">
+        <f aca="false">AB129*($C$20/$C$21)</f>
+        <v>677.18</v>
+      </c>
+      <c r="AC130" s="12" t="n">
+        <f aca="false">AC129*($C$20/$C$21)</f>
+        <v>683.074</v>
+      </c>
+      <c r="AD130" s="12" t="n">
+        <f aca="false">AD129*($C$20/$C$21)</f>
+        <v>663.04</v>
+      </c>
+      <c r="AE130" s="6" t="n">
+        <f aca="false">AE129*($C$32/$C$33)</f>
+        <v>522.08</v>
+      </c>
+      <c r="AF130" s="6" t="n">
+        <f aca="false">AF129*($C$32/$C$33)</f>
+        <v>511.876923076923</v>
+      </c>
+      <c r="AG130" s="6" t="n">
+        <f aca="false">AG129*($C$32/$C$33)</f>
+        <v>503.064615384615</v>
+      </c>
+      <c r="AH130" s="6" t="n">
+        <f aca="false">AH129*($C$32/$C$33)</f>
+        <v>479.2</v>
+      </c>
+      <c r="AI130" s="6" t="n">
+        <f aca="false">AI129*($C$32/$C$33)</f>
+        <v>457.698461538462</v>
+      </c>
+      <c r="AJ130" s="6" t="n">
+        <f aca="false">AJ129*($C$32/$C$33)</f>
+        <v>431.2</v>
+      </c>
+      <c r="AK130" s="6" t="n">
+        <f aca="false">AK129*($C$32/$C$33)</f>
+        <v>406.092307692308</v>
+      </c>
+      <c r="AL130" s="6" t="n">
+        <f aca="false">AL129*($C$32/$C$33)</f>
+        <v>376.923076923077</v>
+      </c>
+      <c r="AM130" s="6" t="n">
+        <f aca="false">AM129*($C$32/$C$33)</f>
+        <v>348.935384615385</v>
+      </c>
+      <c r="AN130" s="6" t="n">
+        <f aca="false">AN129*($C$32/$C$33)</f>
+        <v>321.366153846154</v>
+      </c>
+      <c r="AO130" s="6" t="n">
+        <f aca="false">AO129*($C$32/$C$33)</f>
+        <v>286.018461538462</v>
+      </c>
+      <c r="AP130" s="6" t="n">
+        <f aca="false">AP129*($C$32/$C$33)</f>
+        <v>258.769230769231</v>
+      </c>
+      <c r="AQ130" s="6" t="n">
+        <f aca="false">AQ129*($C$32/$C$33)</f>
+        <v>230.449230769231</v>
+      </c>
+      <c r="AR130" s="6" t="n">
+        <f aca="false">AR129*($C$32/$C$33)</f>
+        <v>203.84</v>
+      </c>
+      <c r="AS130" s="6" t="n">
+        <f aca="false">AS129*($C$32/$C$33)</f>
+        <v>177.661538461538</v>
+      </c>
+      <c r="AT130" s="6" t="n">
+        <f aca="false">AT129*($C$32/$C$33)</f>
+        <v>153.796923076923</v>
+      </c>
+      <c r="AU130" s="6" t="n">
+        <f aca="false">AU129*($C$32/$C$33)</f>
+        <v>131.335384615385</v>
+      </c>
+      <c r="AV130" s="6" t="n">
+        <f aca="false">AV129*($C$32/$C$33)</f>
+        <v>112.664615384615</v>
+      </c>
+      <c r="AW130" s="1" t="n">
+        <f aca="false">AW129*($C$44/$C$45)</f>
+        <v>19.59</v>
+      </c>
+      <c r="AX130" s="6" t="n">
+        <f aca="false">AX129*($C$44/$C$45)</f>
+        <v>19.63</v>
+      </c>
+      <c r="AY130" s="6" t="n">
+        <f aca="false">AY129*($C$44/$C$45)</f>
+        <v>19.3</v>
+      </c>
+      <c r="AZ130" s="6" t="n">
+        <f aca="false">AZ129*($C$44/$C$45)</f>
+        <v>18.89</v>
+      </c>
+      <c r="BA130" s="6" t="n">
+        <f aca="false">BA129*($C$44/$C$45)</f>
+        <v>18.13</v>
+      </c>
+      <c r="BB130" s="6" t="n">
+        <f aca="false">BB129*($C$44/$C$45)</f>
+        <v>17.16</v>
+      </c>
+      <c r="BC130" s="6" t="n">
+        <f aca="false">BC129*($C$44/$C$45)</f>
+        <v>16.07</v>
+      </c>
+      <c r="BD130" s="6" t="n">
+        <f aca="false">BD129*($C$44/$C$45)</f>
+        <v>14.91</v>
+      </c>
+      <c r="BE130" s="6" t="n">
+        <f aca="false">BE129*($C$44/$C$45)</f>
+        <v>12.65</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B131" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C130" s="0" t="s">
+      <c r="C131" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="D130" s="0" t="n">
+      <c r="D131" s="0" t="n">
         <v>10.4</v>
       </c>
-      <c r="E130" s="0" t="n">
+      <c r="E131" s="0" t="n">
         <v>11.1</v>
       </c>
-      <c r="F130" s="0" t="n">
+      <c r="F131" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="G130" s="0" t="n">
+      <c r="G131" s="0" t="n">
         <v>12.9</v>
       </c>
-      <c r="H130" s="0" t="n">
+      <c r="H131" s="0" t="n">
         <v>13.8</v>
       </c>
-      <c r="I130" s="0" t="n">
+      <c r="I131" s="0" t="n">
         <v>14.9</v>
       </c>
-      <c r="J130" s="0" t="n">
+      <c r="J131" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="K130" s="0" t="n">
+      <c r="K131" s="0" t="n">
         <v>17.2</v>
       </c>
-      <c r="L130" s="0" t="n">
+      <c r="L131" s="0" t="n">
         <v>18.4</v>
       </c>
-      <c r="M130" s="0" t="n">
+      <c r="M131" s="0" t="n">
         <v>19.8</v>
       </c>
-      <c r="N130" s="0" t="n">
+      <c r="N131" s="0" t="n">
         <v>21.3</v>
       </c>
-      <c r="O130" s="0" t="n">
+      <c r="O131" s="0" t="n">
         <v>22.9</v>
       </c>
-      <c r="P130" s="0" t="n">
+      <c r="P131" s="0" t="n">
         <v>24.6</v>
       </c>
-      <c r="Q130" s="0" t="n">
+      <c r="Q131" s="0" t="n">
         <v>26.4</v>
       </c>
-      <c r="R130" s="0" t="n">
+      <c r="R131" s="0" t="n">
         <v>28.4</v>
       </c>
-      <c r="S130" s="0" t="n">
+      <c r="S131" s="0" t="n">
         <v>30.5</v>
       </c>
-      <c r="T130" s="0" t="n">
+      <c r="T131" s="0" t="n">
         <v>32.8</v>
       </c>
-      <c r="U130" s="0" t="n">
+      <c r="U131" s="0" t="n">
         <v>35.2</v>
       </c>
-      <c r="V130" s="0" t="n">
+      <c r="V131" s="0" t="n">
         <v>37.9</v>
       </c>
-      <c r="W130" s="0" t="n">
+      <c r="W131" s="0" t="n">
         <v>40.7</v>
       </c>
-      <c r="X130" s="0" t="n">
+      <c r="X131" s="0" t="n">
         <v>43.7</v>
       </c>
-      <c r="Y130" s="0" t="n">
+      <c r="Y131" s="0" t="n">
         <v>47</v>
       </c>
-      <c r="Z130" s="0" t="n">
+      <c r="Z131" s="0" t="n">
         <v>50.5</v>
       </c>
-      <c r="AA130" s="0" t="n">
+      <c r="AA131" s="0" t="n">
         <v>54.2</v>
       </c>
-      <c r="AB130" s="0" t="n">
+      <c r="AB131" s="0" t="n">
         <v>58.3</v>
       </c>
-      <c r="AC130" s="0" t="n">
+      <c r="AC131" s="0" t="n">
         <v>62.6</v>
       </c>
-      <c r="AD130" s="0" t="n">
+      <c r="AD131" s="0" t="n">
         <v>67.3</v>
       </c>
-      <c r="AE130" s="0" t="n">
+      <c r="AE131" s="0" t="n">
         <v>72.3</v>
       </c>
-      <c r="AF130" s="0" t="n">
+      <c r="AF131" s="0" t="n">
         <v>77.7</v>
       </c>
-      <c r="AG130" s="0" t="n">
+      <c r="AG131" s="0" t="n">
         <v>83.5</v>
       </c>
-      <c r="AH130" s="0" t="n">
+      <c r="AH131" s="0" t="n">
         <v>89.8</v>
       </c>
-      <c r="AI130" s="0" t="n">
+      <c r="AI131" s="0" t="n">
         <v>96.5</v>
       </c>
-      <c r="AJ130" s="0" t="n">
+      <c r="AJ131" s="0" t="n">
         <v>103.7</v>
       </c>
-      <c r="AK130" s="0" t="n">
+      <c r="AK131" s="0" t="n">
         <v>111.4</v>
       </c>
-      <c r="AL130" s="0" t="n">
+      <c r="AL131" s="0" t="n">
         <v>119.7</v>
       </c>
-      <c r="AM130" s="0" t="n">
+      <c r="AM131" s="0" t="n">
         <v>128.6</v>
       </c>
-      <c r="AN130" s="0" t="n">
+      <c r="AN131" s="0" t="n">
         <v>138.2</v>
       </c>
-      <c r="AO130" s="0" t="n">
+      <c r="AO131" s="0" t="n">
         <v>148.6</v>
       </c>
-      <c r="AP130" s="0" t="n">
+      <c r="AP131" s="0" t="n">
         <v>159.6</v>
       </c>
-      <c r="AQ130" s="0" t="n">
+      <c r="AQ131" s="0" t="n">
         <v>171.5</v>
       </c>
-      <c r="AR130" s="0" t="n">
+      <c r="AR131" s="0" t="n">
         <v>184.3</v>
       </c>
-      <c r="AS130" s="0" t="n">
+      <c r="AS131" s="0" t="n">
         <v>198.1</v>
       </c>
-      <c r="AT130" s="0" t="n">
+      <c r="AT131" s="0" t="n">
         <v>212.9</v>
       </c>
-      <c r="AU130" s="0" t="n">
+      <c r="AU131" s="0" t="n">
         <v>228.8</v>
       </c>
-      <c r="AV130" s="0" t="n">
+      <c r="AV131" s="0" t="n">
         <v>245.8</v>
       </c>
-      <c r="AW130" s="2" t="n">
+      <c r="AW131" s="2" t="n">
         <v>264.2</v>
       </c>
-      <c r="AX130" s="0" t="n">
+      <c r="AX131" s="0" t="n">
         <v>283.9</v>
       </c>
-      <c r="AY130" s="0" t="n">
+      <c r="AY131" s="0" t="n">
         <v>305.1</v>
       </c>
-      <c r="AZ130" s="0" t="n">
+      <c r="AZ131" s="0" t="n">
         <v>327.8</v>
       </c>
-      <c r="BA130" s="0" t="n">
+      <c r="BA131" s="0" t="n">
         <v>352.3</v>
       </c>
-      <c r="BB130" s="0" t="n">
+      <c r="BB131" s="0" t="n">
         <v>378.6</v>
       </c>
-      <c r="BC130" s="0" t="n">
+      <c r="BC131" s="0" t="n">
         <v>406.8</v>
       </c>
-      <c r="BD130" s="0" t="n">
+      <c r="BD131" s="0" t="n">
         <v>437.1</v>
       </c>
-      <c r="BE130" s="0" t="n">
+      <c r="BE131" s="0" t="n">
         <v>469.8</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="132" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -8730,7 +8695,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F55"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="14.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.28"/>
@@ -8742,16 +8707,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
